--- a/consumo_628.xlsx
+++ b/consumo_628.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Departamentos\Contabilidad\03 Suministros_consumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538435FF-FEAD-4AC1-AE3A-CF6904A5E247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0B47AF-D7B2-4B18-BDDE-84D7E59D2645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frio cierre 25" sheetId="14" r:id="rId1"/>
@@ -499,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -618,6 +618,8 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -633,9 +635,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2294,13 +2293,13 @@
         <v>78000</v>
       </c>
       <c r="P7" s="39"/>
-      <c r="R7" s="85" t="s">
+      <c r="R7" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
+      <c r="S7" s="87"/>
+      <c r="T7" s="87"/>
+      <c r="U7" s="87"/>
+      <c r="V7" s="87"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -2590,11 +2589,11 @@
         <v>276673.54100185522</v>
       </c>
       <c r="P12" s="39"/>
-      <c r="R12" s="82" t="s">
+      <c r="R12" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="S12" s="83"/>
-      <c r="T12" s="84"/>
+      <c r="S12" s="85"/>
+      <c r="T12" s="86"/>
       <c r="U12" s="47">
         <f>+U10*S9</f>
         <v>-8283.0026496869687</v>
@@ -2616,11 +2615,11 @@
       <c r="N13" s="39"/>
       <c r="O13" s="20"/>
       <c r="P13" s="39"/>
-      <c r="R13" s="82" t="s">
+      <c r="R13" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="S13" s="83"/>
-      <c r="T13" s="84"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="86"/>
       <c r="U13" s="47">
         <f>+U9*T10</f>
         <v>-5990.1364407635365</v>
@@ -2820,13 +2819,13 @@
         <v>2160.91</v>
       </c>
       <c r="P18" s="39"/>
-      <c r="R18" s="86" t="s">
+      <c r="R18" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -3134,11 +3133,11 @@
         <v>71999.000000000015</v>
       </c>
       <c r="P23" s="39"/>
-      <c r="R23" s="82" t="s">
+      <c r="R23" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="83"/>
-      <c r="T23" s="84"/>
+      <c r="S23" s="85"/>
+      <c r="T23" s="86"/>
       <c r="U23" s="47">
         <f>+U21*S20</f>
         <v>-33537.857501708335</v>
@@ -3160,11 +3159,11 @@
       <c r="N24" s="39"/>
       <c r="O24" s="20"/>
       <c r="P24" s="39"/>
-      <c r="R24" s="82" t="s">
+      <c r="R24" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="S24" s="83"/>
-      <c r="T24" s="84"/>
+      <c r="S24" s="85"/>
+      <c r="T24" s="86"/>
       <c r="U24" s="47">
         <f>+U20*T21</f>
         <v>13037.816139863742</v>
@@ -3478,6 +3477,7 @@
     <col min="14" max="14" width="3.28515625" customWidth="1"/>
     <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.28515625" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3558,15 +3558,18 @@
         <f t="shared" si="2"/>
         <v>158.72</v>
       </c>
-      <c r="I5" s="20"/>
+      <c r="I5" s="20">
+        <f t="shared" ref="I5" si="3">+I18</f>
+        <v>153.19999999999999</v>
+      </c>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
       <c r="N5" s="39"/>
       <c r="O5" s="20">
-        <f t="shared" ref="O5:O10" si="3">SUM(B5:N5)</f>
-        <v>1018.3299999999999</v>
+        <f t="shared" ref="O5:O10" si="4">SUM(B5:N5)</f>
+        <v>1171.53</v>
       </c>
       <c r="P5" s="39"/>
     </row>
@@ -3587,30 +3590,33 @@
         <v>35.055460618300451</v>
       </c>
       <c r="E6" s="20">
-        <f t="shared" ref="E6:F6" si="4">+E19</f>
+        <f t="shared" ref="E6:F6" si="5">+E19</f>
         <v>40.414212174282227</v>
       </c>
       <c r="F6" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>34.383172917358117</v>
       </c>
       <c r="G6" s="20">
-        <f t="shared" ref="G6:H6" si="5">+G19</f>
+        <f t="shared" ref="G6:H6" si="6">+G19</f>
         <v>40.921465025517861</v>
       </c>
       <c r="H6" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>55.163684475806448</v>
       </c>
-      <c r="I6" s="20"/>
+      <c r="I6" s="20">
+        <f t="shared" ref="I6" si="7">+I19</f>
+        <v>60.109856396866846</v>
+      </c>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" s="39"/>
       <c r="O6" s="20">
-        <f t="shared" si="3"/>
-        <v>322.9045961115645</v>
+        <f t="shared" si="4"/>
+        <v>383.01445250843136</v>
       </c>
       <c r="P6" s="39"/>
     </row>
@@ -3646,24 +3652,27 @@
         <f>6500</f>
         <v>6500</v>
       </c>
-      <c r="I7" s="41"/>
+      <c r="I7" s="41">
+        <f>6500</f>
+        <v>6500</v>
+      </c>
       <c r="J7" s="41"/>
       <c r="K7" s="41"/>
       <c r="L7" s="41"/>
       <c r="M7" s="41"/>
       <c r="N7" s="39"/>
       <c r="O7" s="41">
-        <f t="shared" si="3"/>
-        <v>45500</v>
+        <f t="shared" si="4"/>
+        <v>52000</v>
       </c>
       <c r="P7" s="39"/>
-      <c r="R7" s="85" t="s">
+      <c r="R7" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
+      <c r="S7" s="87"/>
+      <c r="T7" s="87"/>
+      <c r="U7" s="87"/>
+      <c r="V7" s="87"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -3690,15 +3699,17 @@
       <c r="H8" s="41">
         <v>8031.0312000000004</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="41">
+        <v>8031.0312000000004</v>
+      </c>
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="41"/>
       <c r="N8" s="39"/>
       <c r="O8" s="41">
-        <f t="shared" si="3"/>
-        <v>56217.218399999998</v>
+        <f t="shared" si="4"/>
+        <v>64248.249599999996</v>
       </c>
       <c r="P8" s="39"/>
       <c r="S8" s="42" t="s">
@@ -3736,15 +3747,17 @@
       <c r="H9" s="41">
         <v>2100</v>
       </c>
-      <c r="I9" s="41"/>
+      <c r="I9" s="41">
+        <v>2100</v>
+      </c>
       <c r="J9" s="41"/>
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
       <c r="M9" s="41"/>
       <c r="N9" s="39"/>
       <c r="O9" s="41">
-        <f t="shared" si="3"/>
-        <v>14700</v>
+        <f t="shared" si="4"/>
+        <v>16800</v>
       </c>
       <c r="P9" s="39"/>
       <c r="R9" s="43" t="s">
@@ -3752,22 +3765,22 @@
       </c>
       <c r="S9" s="44">
         <f>+O18*1000</f>
-        <v>1018329.9999999999</v>
+        <v>1171530</v>
       </c>
       <c r="T9" s="44">
         <f>+X9</f>
-        <v>1113815</v>
+        <v>1501840</v>
       </c>
       <c r="U9" s="44">
         <f>+T9-S9</f>
-        <v>95485.000000000116</v>
+        <v>330310</v>
       </c>
       <c r="V9" s="45">
         <f>+U9/T9</f>
-        <v>8.5727881201097228E-2</v>
+        <v>0.21993687743035209</v>
       </c>
       <c r="X9" s="3">
-        <v>1113815</v>
+        <v>1501840</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -3795,33 +3808,35 @@
       <c r="H10" s="41">
         <v>6200</v>
       </c>
-      <c r="I10" s="41"/>
+      <c r="I10" s="41">
+        <v>6200</v>
+      </c>
       <c r="J10" s="41"/>
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
       <c r="M10" s="41"/>
       <c r="N10" s="39"/>
       <c r="O10" s="41">
-        <f t="shared" si="3"/>
-        <v>43400</v>
+        <f t="shared" si="4"/>
+        <v>49600</v>
       </c>
       <c r="P10" s="39"/>
       <c r="R10" s="43" t="s">
         <v>35</v>
       </c>
       <c r="S10" s="46">
-        <v>0.13072642650164179</v>
+        <v>0.13914603105996484</v>
       </c>
       <c r="T10" s="46">
-        <v>0.12569478865166375</v>
+        <v>0.12661887429000285</v>
       </c>
       <c r="U10" s="46">
         <f>+T10-S10</f>
-        <v>-5.0316378499780379E-3</v>
+        <v>-1.2527156769961995E-2</v>
       </c>
       <c r="V10" s="45">
         <f>+U10/T10</f>
-        <v>-4.0030600345111737E-2</v>
+        <v>-9.8935935421999494E-2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -3846,67 +3861,67 @@
         <v>36</v>
       </c>
       <c r="B12" s="21">
-        <f t="shared" ref="B12:M12" si="6">SUM(B7:B11)</f>
+        <f t="shared" ref="B12:M12" si="8">SUM(B7:B11)</f>
         <v>22831.031200000001</v>
       </c>
       <c r="C12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="D12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="E12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="F12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="G12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="H12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22831.031200000001</v>
       </c>
       <c r="I12" s="21">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>22831.031200000001</v>
       </c>
       <c r="J12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N12" s="39"/>
       <c r="O12" s="21">
         <f>SUM(O7:O11)</f>
-        <v>159817.21840000001</v>
+        <v>182648.24959999998</v>
       </c>
       <c r="P12" s="39"/>
-      <c r="R12" s="82" t="s">
+      <c r="R12" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="S12" s="83"/>
-      <c r="T12" s="84"/>
+      <c r="S12" s="85"/>
+      <c r="T12" s="86"/>
       <c r="U12" s="47">
         <f>+U10*S9</f>
-        <v>-5123.8677717681348</v>
+        <v>-14675.939970713576</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -3925,14 +3940,14 @@
       <c r="N13" s="39"/>
       <c r="O13" s="20"/>
       <c r="P13" s="39"/>
-      <c r="R13" s="82" t="s">
+      <c r="R13" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="S13" s="83"/>
-      <c r="T13" s="84"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="86"/>
       <c r="U13" s="47">
         <f>+U9*T10</f>
-        <v>12001.966894404128</v>
+        <v>41823.480366730837</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3940,62 +3955,62 @@
         <v>14</v>
       </c>
       <c r="B14" s="20">
-        <f t="shared" ref="B14:M14" si="7">+B7+B8</f>
+        <f t="shared" ref="B14:M14" si="9">+B7+B8</f>
         <v>14531.031200000001</v>
       </c>
       <c r="C14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="D14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="E14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="F14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="G14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="H14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14531.031200000001</v>
       </c>
       <c r="I14" s="20">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>14531.031200000001</v>
       </c>
       <c r="J14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M14" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N14" s="39"/>
       <c r="O14" s="20">
         <f>+O7+O8</f>
-        <v>101717.2184</v>
+        <v>116248.2496</v>
       </c>
       <c r="P14" s="39"/>
       <c r="U14" s="48">
         <f>SUM(U12:U13)</f>
-        <v>6878.0991226359929</v>
+        <v>27147.540396017263</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -4015,8 +4030,8 @@
       <c r="O15" s="20"/>
       <c r="P15" s="39"/>
       <c r="U15" s="49">
-        <f>+U14-27627</f>
-        <v>-20748.900877364009</v>
+        <f>+U14-27148</f>
+        <v>-0.4596039827374625</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -4108,7 +4123,9 @@
       <c r="H18" s="20">
         <v>158.72</v>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="20">
+        <v>153.19999999999999</v>
+      </c>
       <c r="J18" s="20"/>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
@@ -4116,16 +4133,16 @@
       <c r="N18" s="39"/>
       <c r="O18" s="20">
         <f>SUM(B18:N18)</f>
-        <v>1018.3299999999999</v>
+        <v>1171.53</v>
       </c>
       <c r="P18" s="39"/>
-      <c r="R18" s="86" t="s">
+      <c r="R18" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -4159,7 +4176,10 @@
         <f>8755.58/H18</f>
         <v>55.163684475806448</v>
       </c>
-      <c r="I19" s="20"/>
+      <c r="I19" s="20">
+        <f>9208.83/I18</f>
+        <v>60.109856396866846</v>
+      </c>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
       <c r="L19" s="20"/>
@@ -4167,7 +4187,7 @@
       <c r="N19" s="39"/>
       <c r="O19" s="20">
         <f>+O20/O18</f>
-        <v>44.497923070124621</v>
+        <v>46.539482556998117</v>
       </c>
       <c r="P19" s="39"/>
       <c r="S19" s="42" t="s">
@@ -4185,19 +4205,19 @@
         <v>26</v>
       </c>
       <c r="B20" s="20">
-        <f t="shared" ref="B20:E20" si="8">+B18*B19</f>
+        <f t="shared" ref="B20:E20" si="10">+B18*B19</f>
         <v>7260.61</v>
       </c>
       <c r="C20" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4137.83</v>
       </c>
       <c r="D20" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4513.04</v>
       </c>
       <c r="E20" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7615.25</v>
       </c>
       <c r="F20" s="20">
@@ -4209,7 +4229,9 @@
       <c r="H20" s="20">
         <v>8755.58</v>
       </c>
-      <c r="I20" s="20"/>
+      <c r="I20" s="20">
+        <v>9208.83</v>
+      </c>
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
@@ -4217,7 +4239,7 @@
       <c r="N20" s="39"/>
       <c r="O20" s="20">
         <f>SUM(B20:N20)</f>
-        <v>45313.57</v>
+        <v>54522.400000000001</v>
       </c>
       <c r="P20" s="39"/>
       <c r="R20" s="43" t="s">
@@ -4225,22 +4247,22 @@
       </c>
       <c r="S20" s="1">
         <f>+S9</f>
-        <v>1018329.9999999999</v>
+        <v>1171530</v>
       </c>
       <c r="T20" s="1">
         <f>+X20</f>
-        <v>964350</v>
+        <v>1426820</v>
       </c>
       <c r="U20" s="44">
         <f>+T20-S20</f>
-        <v>-53979.999999999884</v>
+        <v>255290</v>
       </c>
       <c r="V20" s="45">
         <f>+U20/T20</f>
-        <v>-5.5975527557421974E-2</v>
+        <v>0.17892235881190338</v>
       </c>
       <c r="X20" s="3">
-        <v>964350</v>
+        <v>1426820</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -4268,7 +4290,9 @@
       <c r="H21" s="20">
         <v>8841.9500000000007</v>
       </c>
-      <c r="I21" s="20"/>
+      <c r="I21" s="20">
+        <v>8841.9500000000007</v>
+      </c>
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
@@ -4276,25 +4300,25 @@
       <c r="N21" s="39"/>
       <c r="O21" s="20">
         <f>SUM(B21:N21)</f>
-        <v>61893.649999999994</v>
+        <v>70735.599999999991</v>
       </c>
       <c r="P21" s="39"/>
       <c r="R21" s="43" t="s">
         <v>35</v>
       </c>
       <c r="S21" s="46">
-        <v>0.13072642650164179</v>
+        <v>0.13914603105996484</v>
       </c>
       <c r="T21" s="46">
-        <v>0.12485467469406245</v>
+        <v>0.12405122345077409</v>
       </c>
       <c r="U21" s="46">
         <f>+T21-S21</f>
-        <v>-5.8717518075793451E-3</v>
+        <v>-1.5094807609190755E-2</v>
       </c>
       <c r="V21" s="45">
         <f>+U21/T21</f>
-        <v>-4.7028690130883663E-2</v>
+        <v>-0.12168205350413706</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -4322,7 +4346,9 @@
       <c r="H22" s="20">
         <v>2003.09</v>
       </c>
-      <c r="I22" s="20"/>
+      <c r="I22" s="20">
+        <v>1979.55</v>
+      </c>
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
@@ -4330,7 +4356,7 @@
       <c r="N22" s="39"/>
       <c r="O22" s="20">
         <f>SUM(B22:N22)</f>
-        <v>14534.449999999999</v>
+        <v>16514</v>
       </c>
       <c r="P22" s="39"/>
     </row>
@@ -4359,7 +4385,9 @@
       <c r="H23" s="20">
         <v>6285.75</v>
       </c>
-      <c r="I23" s="20"/>
+      <c r="I23" s="20">
+        <v>6309.29</v>
+      </c>
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -4367,17 +4395,17 @@
       <c r="N23" s="39"/>
       <c r="O23" s="20">
         <f>SUM(B23:N23)</f>
-        <v>43487.42</v>
+        <v>49796.71</v>
       </c>
       <c r="P23" s="39"/>
-      <c r="R23" s="82" t="s">
+      <c r="R23" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="83"/>
-      <c r="T23" s="84"/>
+      <c r="S23" s="85"/>
+      <c r="T23" s="86"/>
       <c r="U23" s="47">
         <f>+U21*S20</f>
-        <v>-5979.3810182122743</v>
+        <v>-17684.019958395245</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -4396,14 +4424,14 @@
       <c r="N24" s="39"/>
       <c r="O24" s="20"/>
       <c r="P24" s="39"/>
-      <c r="R24" s="82" t="s">
+      <c r="R24" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="S24" s="83"/>
-      <c r="T24" s="84"/>
+      <c r="S24" s="85"/>
+      <c r="T24" s="86"/>
       <c r="U24" s="47">
         <f>+U20*T21</f>
-        <v>-6739.6553399854765</v>
+        <v>31669.036834748116</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -4411,62 +4439,62 @@
         <v>36</v>
       </c>
       <c r="B25" s="21">
-        <f t="shared" ref="B25:M25" si="9">SUM(B20:B24)</f>
+        <f t="shared" ref="B25:M25" si="11">SUM(B20:B24)</f>
         <v>24391.4</v>
       </c>
       <c r="C25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>21268.62</v>
       </c>
       <c r="D25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>21643.83</v>
       </c>
       <c r="E25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>24746.03</v>
       </c>
       <c r="F25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>23346.58</v>
       </c>
       <c r="G25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>23946.260000000002</v>
       </c>
       <c r="H25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>25886.37</v>
       </c>
       <c r="I25" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>26339.62</v>
       </c>
       <c r="J25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M25" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="N25" s="39"/>
       <c r="O25" s="21">
         <f>SUM(O20:O24)</f>
-        <v>165229.09</v>
+        <v>191568.71</v>
       </c>
       <c r="P25" s="39"/>
       <c r="U25" s="48">
         <f>SUM(U23:U24)</f>
-        <v>-12719.036358197751</v>
+        <v>13985.016876352871</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -4486,8 +4514,8 @@
       <c r="O26" s="20"/>
       <c r="P26" s="39"/>
       <c r="U26" s="49">
-        <f>+U25-8029.65</f>
-        <v>-20748.686358197752</v>
+        <f>+U25-13985</f>
+        <v>1.6876352870895062E-2</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -4495,57 +4523,57 @@
         <v>14</v>
       </c>
       <c r="B27" s="20">
-        <f t="shared" ref="B27:M27" si="10">+B20+B21</f>
+        <f t="shared" ref="B27:M27" si="12">+B20+B21</f>
         <v>16102.560000000001</v>
       </c>
       <c r="C27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12979.78</v>
       </c>
       <c r="D27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13354.990000000002</v>
       </c>
       <c r="E27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>16457.2</v>
       </c>
       <c r="F27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>15057.740000000002</v>
       </c>
       <c r="G27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>15657.420000000002</v>
       </c>
       <c r="H27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>17597.53</v>
       </c>
       <c r="I27" s="20">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>18050.78</v>
       </c>
       <c r="J27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M27" s="20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N27" s="39"/>
       <c r="O27" s="20">
         <f>+O20+O21</f>
-        <v>107207.22</v>
+        <v>125258</v>
       </c>
       <c r="P27" s="39"/>
       <c r="U27">
@@ -4562,53 +4590,53 @@
         <v>1571.5288</v>
       </c>
       <c r="C29" s="20">
-        <f t="shared" ref="C29:M29" si="11">+C27-C14</f>
+        <f t="shared" ref="C29:M29" si="13">+C27-C14</f>
         <v>-1551.2512000000006</v>
       </c>
       <c r="D29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1176.0411999999997</v>
       </c>
       <c r="E29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1926.1687999999995</v>
       </c>
       <c r="F29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>526.70880000000034</v>
       </c>
       <c r="G29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1126.3888000000006</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3066.4987999999976</v>
       </c>
       <c r="I29" s="20">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>3519.7487999999976</v>
       </c>
       <c r="J29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M29" s="20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N29" s="39"/>
       <c r="O29" s="20">
         <f>+O14-O27</f>
-        <v>-5490.0016000000032</v>
+        <v>-9009.7504000000044</v>
       </c>
       <c r="P29" s="39"/>
     </row>
@@ -4622,44 +4650,44 @@
         <v>20.277599999999438</v>
       </c>
       <c r="D30" s="20">
-        <f t="shared" ref="D30:M30" si="12">+C30+D29</f>
+        <f t="shared" ref="D30:M30" si="14">+C30+D29</f>
         <v>-1155.7636000000002</v>
       </c>
       <c r="E30" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>770.40519999999924</v>
       </c>
       <c r="F30" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1297.1139999999996</v>
       </c>
       <c r="G30" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2423.5028000000002</v>
       </c>
       <c r="H30" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5490.0015999999978</v>
       </c>
       <c r="I30" s="20">
-        <f t="shared" si="12"/>
-        <v>5490.0015999999978</v>
+        <f t="shared" si="14"/>
+        <v>9009.7503999999954</v>
       </c>
       <c r="J30" s="20">
-        <f t="shared" si="12"/>
-        <v>5490.0015999999978</v>
+        <f t="shared" si="14"/>
+        <v>9009.7503999999954</v>
       </c>
       <c r="K30" s="20">
-        <f t="shared" si="12"/>
-        <v>5490.0015999999978</v>
+        <f t="shared" si="14"/>
+        <v>9009.7503999999954</v>
       </c>
       <c r="L30" s="20">
-        <f t="shared" si="12"/>
-        <v>5490.0015999999978</v>
+        <f t="shared" si="14"/>
+        <v>9009.7503999999954</v>
       </c>
       <c r="M30" s="20">
-        <f t="shared" si="12"/>
-        <v>5490.0015999999978</v>
+        <f t="shared" si="14"/>
+        <v>9009.7503999999954</v>
       </c>
       <c r="N30" s="39"/>
       <c r="O30" s="20"/>
@@ -7258,11 +7286,13 @@
       <c r="K4" s="6">
         <v>6</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="4">
+        <v>4</v>
+      </c>
       <c r="M4" s="5"/>
       <c r="N4" s="7">
         <f>SUM(K4:M4)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="4"/>
@@ -7273,7 +7303,7 @@
       </c>
       <c r="S4" s="7">
         <f>F4+J4+N4+R4</f>
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7309,11 +7339,13 @@
       <c r="K5" s="11">
         <v>116572.19</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="11">
+        <v>64950.99</v>
+      </c>
       <c r="M5" s="11"/>
       <c r="N5" s="13">
         <f>SUM(K5:M5)</f>
-        <v>116572.19</v>
+        <v>181523.18</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
@@ -7324,7 +7356,7 @@
       </c>
       <c r="S5" s="13">
         <f>F5+J5+N5+R5</f>
-        <v>1670190.6199999996</v>
+        <v>1735141.6099999996</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -7385,14 +7417,14 @@
         <f>SUM(G9:I9)</f>
         <v>1199378</v>
       </c>
-      <c r="K9" s="87">
-        <v>275812</v>
+      <c r="K9" s="9">
+        <v>219535</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="8"/>
       <c r="N9" s="10">
         <f>SUM(K9:M9)</f>
-        <v>275812</v>
+        <v>219535</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="1"/>
@@ -7403,7 +7435,7 @@
       </c>
       <c r="S9" s="10">
         <f>F9+J9+N9+R9</f>
-        <v>2884911</v>
+        <v>2828634</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7436,14 +7468,14 @@
         <f>SUM(G10:I10)</f>
         <v>56623.509999999995</v>
       </c>
-      <c r="K10" s="88">
-        <v>14888.47</v>
+      <c r="K10" s="14">
+        <v>11531.83</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="12"/>
       <c r="N10" s="13">
         <f>SUM(K10:M10)</f>
-        <v>14888.47</v>
+        <v>11531.83</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11"/>
@@ -7454,7 +7486,7 @@
       </c>
       <c r="S10" s="13">
         <f>F10+J10+N10+R10</f>
-        <v>133599.66999999998</v>
+        <v>130243.03</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7495,13 +7527,13 @@
       </c>
       <c r="K11" s="37">
         <f>+K10/K9</f>
-        <v>5.398050121096979E-2</v>
+        <v>5.252843510146446E-2</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="13">
         <f t="shared" si="0"/>
-        <v>5.398050121096979E-2</v>
+        <v>5.252843510146446E-2</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7512,7 +7544,7 @@
       </c>
       <c r="S11" s="13">
         <f t="shared" si="0"/>
-        <v>4.6309806437702924E-2</v>
+        <v>4.6044497096478371E-2</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7565,11 +7597,11 @@
       </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
-        <v>45968.666666666664</v>
-      </c>
-      <c r="L13" s="1" t="e">
+        <v>36589.166666666664</v>
+      </c>
+      <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1" t="e">
         <f t="shared" si="1"/>
@@ -7577,7 +7609,7 @@
       </c>
       <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>45968.666666666664</v>
+        <v>21953.5</v>
       </c>
       <c r="O13" s="1" t="e">
         <f t="shared" si="1"/>
@@ -7597,7 +7629,7 @@
       </c>
       <c r="S13" s="10">
         <f t="shared" si="1"/>
-        <v>41213.014285714286</v>
+        <v>38224.783783783787</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7641,11 +7673,11 @@
       </c>
       <c r="K14" s="11">
         <f t="shared" si="2"/>
-        <v>2481.4116666666664</v>
-      </c>
-      <c r="L14" s="11" t="e">
+        <v>1921.9716666666666</v>
+      </c>
+      <c r="L14" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M14" s="11" t="e">
         <f t="shared" si="2"/>
@@ -7653,7 +7685,7 @@
       </c>
       <c r="N14" s="13">
         <f t="shared" si="2"/>
-        <v>2481.4116666666664</v>
+        <v>1153.183</v>
       </c>
       <c r="O14" s="11" t="e">
         <f t="shared" si="2"/>
@@ -7673,7 +7705,7 @@
       </c>
       <c r="S14" s="13">
         <f t="shared" si="2"/>
-        <v>1908.5667142857139</v>
+        <v>1760.0409459459459</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7717,11 +7749,11 @@
       </c>
       <c r="K15" s="23">
         <f t="shared" si="3"/>
-        <v>2.3660188592150493</v>
-      </c>
-      <c r="L15" s="23" t="e">
+        <v>1.8832536302183223</v>
+      </c>
+      <c r="L15" s="23">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M15" s="23" t="e">
         <f t="shared" si="3"/>
@@ -7729,7 +7761,7 @@
       </c>
       <c r="N15" s="24">
         <f t="shared" si="3"/>
-        <v>2.3660188592150493</v>
+        <v>1.2094047713355396</v>
       </c>
       <c r="O15" s="23" t="e">
         <f t="shared" si="3"/>
@@ -7749,7 +7781,7 @@
       </c>
       <c r="S15" s="24">
         <f>+S9/S5</f>
-        <v>1.7272944569644395</v>
+        <v>1.6302035428681816</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7793,11 +7825,11 @@
       </c>
       <c r="K16" s="18">
         <f t="shared" si="4"/>
-        <v>0.12771888389503533</v>
-      </c>
-      <c r="L16" s="18" t="e">
+        <v>9.8924366094520488E-2</v>
+      </c>
+      <c r="L16" s="18">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M16" s="18" t="e">
         <f t="shared" si="4"/>
@@ -7805,7 +7837,7 @@
       </c>
       <c r="N16" s="19">
         <f t="shared" si="4"/>
-        <v>0.12771888389503533</v>
+        <v>6.3528140042500361E-2</v>
       </c>
       <c r="O16" s="18" t="e">
         <f t="shared" si="4"/>
@@ -7825,7 +7857,7 @@
       </c>
       <c r="S16" s="19">
         <f t="shared" si="4"/>
-        <v>7.999067196294038E-2</v>
+        <v>7.5061902296262736E-2</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
@@ -7867,7 +7899,7 @@
         <f>SUM(G19:I19)</f>
         <v>19672</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="82">
         <v>4688</v>
       </c>
       <c r="L19" s="9"/>
@@ -7921,7 +7953,7 @@
         <f>SUM(G20:I20)</f>
         <v>51328.08</v>
       </c>
-      <c r="K20" s="88">
+      <c r="K20" s="83">
         <v>12376.32</v>
       </c>
       <c r="L20" s="14"/>
@@ -8057,9 +8089,9 @@
         <f t="shared" si="6"/>
         <v>781.33333333333337</v>
       </c>
-      <c r="L22" s="1" t="e">
+      <c r="L22" s="1">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M22" s="1" t="e">
         <f t="shared" si="6"/>
@@ -8067,7 +8099,7 @@
       </c>
       <c r="N22" s="13">
         <f>+N19/N4</f>
-        <v>781.33333333333337</v>
+        <v>468.8</v>
       </c>
       <c r="O22" s="1" t="e">
         <f t="shared" ref="O22:Q22" si="7">+O19/O4</f>
@@ -8087,7 +8119,7 @@
       </c>
       <c r="S22" s="13">
         <f>+S19/S4</f>
-        <v>571.97142857142853</v>
+        <v>541.05405405405406</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8133,9 +8165,9 @@
         <f t="shared" si="8"/>
         <v>2062.7199999999998</v>
       </c>
-      <c r="L23" s="11" t="e">
+      <c r="L23" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M23" s="11" t="e">
         <f t="shared" si="8"/>
@@ -8143,7 +8175,7 @@
       </c>
       <c r="N23" s="13">
         <f>+N20/N4</f>
-        <v>2062.7199999999998</v>
+        <v>1237.6320000000001</v>
       </c>
       <c r="O23" s="11" t="e">
         <f t="shared" ref="O23:Q23" si="9">+O20/O4</f>
@@ -8163,7 +8195,7 @@
       </c>
       <c r="S23" s="13">
         <f>+S20/S4</f>
-        <v>1425.5450337087207</v>
+        <v>1348.4885454001412</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8209,9 +8241,9 @@
         <f t="shared" si="10"/>
         <v>4.021542359288266E-2</v>
       </c>
-      <c r="L24" s="16" t="e">
+      <c r="L24" s="16">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M24" s="16" t="e">
         <f t="shared" si="10"/>
@@ -8219,7 +8251,7 @@
       </c>
       <c r="N24" s="24">
         <f>+N19/N5</f>
-        <v>4.021542359288266E-2</v>
+        <v>2.582590278552855E-2</v>
       </c>
       <c r="O24" s="16" t="e">
         <f t="shared" ref="O24:Q24" si="11">+O19/O5</f>
@@ -8239,7 +8271,7 @@
       </c>
       <c r="S24" s="24">
         <f>+S19/S5</f>
-        <v>2.3972114033307172E-2</v>
+        <v>2.3074773706798495E-2</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8285,9 +8317,9 @@
         <f t="shared" si="12"/>
         <v>0.10616871828521021</v>
       </c>
-      <c r="L25" s="16" t="e">
+      <c r="L25" s="16">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M25" s="16" t="e">
         <f t="shared" si="12"/>
@@ -8295,7 +8327,7 @@
       </c>
       <c r="N25" s="19">
         <f>+N20/N5</f>
-        <v>0.10616871828521021</v>
+        <v>6.8180383353795365E-2</v>
       </c>
       <c r="O25" s="16" t="e">
         <f t="shared" ref="O25:Q25" si="13">+O20/O5</f>
@@ -8315,7 +8347,7 @@
       </c>
       <c r="S25" s="19">
         <f>+S20/S5</f>
-        <v>5.974656495173615E-2</v>
+        <v>5.751009127123087E-2</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -8376,11 +8408,13 @@
       <c r="K28" s="9">
         <v>243627</v>
       </c>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1">
+        <v>226202</v>
+      </c>
       <c r="M28" s="8"/>
       <c r="N28" s="10">
         <f>SUM(K28:M28)</f>
-        <v>243627</v>
+        <v>469829</v>
       </c>
       <c r="O28" s="9"/>
       <c r="P28" s="1"/>
@@ -8391,7 +8425,7 @@
       </c>
       <c r="S28" s="10">
         <f>F28+J28+N28+R28</f>
-        <v>1772770</v>
+        <v>1998972</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8424,14 +8458,14 @@
         <f>SUM(G29:I29)</f>
         <v>91418.7</v>
       </c>
-      <c r="K29" s="89">
-        <v>31671.51</v>
+      <c r="K29" s="12">
+        <v>45013.9</v>
       </c>
       <c r="L29" s="11"/>
       <c r="M29" s="12"/>
       <c r="N29" s="13">
         <f>SUM(K29:M29)</f>
-        <v>31671.51</v>
+        <v>45013.9</v>
       </c>
       <c r="O29" s="14"/>
       <c r="P29" s="11"/>
@@ -8442,7 +8476,7 @@
       </c>
       <c r="S29" s="13">
         <f>F29+J29+N29+R29</f>
-        <v>211676.58000000002</v>
+        <v>225018.97</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8481,12 +8515,15 @@
         <f t="shared" si="14"/>
         <v>0.10931681400690922</v>
       </c>
-      <c r="K30" s="11"/>
+      <c r="K30" s="11">
+        <f>+K29/K28</f>
+        <v>0.18476564584385147</v>
+      </c>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="13">
         <f t="shared" si="14"/>
-        <v>0.13</v>
+        <v>9.5809113528539117E-2</v>
       </c>
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
@@ -8497,7 +8534,7 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="14"/>
-        <v>0.11940442358568794</v>
+        <v>0.11256734461513218</v>
       </c>
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
@@ -8510,6 +8547,7 @@
       <c r="G31" s="20"/>
       <c r="I31" s="20"/>
       <c r="J31" s="32"/>
+      <c r="K31" s="20"/>
       <c r="N31" s="32"/>
       <c r="R31" s="32"/>
       <c r="S31" s="32"/>
@@ -8557,9 +8595,9 @@
         <f t="shared" si="15"/>
         <v>40604.5</v>
       </c>
-      <c r="L32" s="1" t="e">
+      <c r="L32" s="1">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>56550.5</v>
       </c>
       <c r="M32" s="1" t="e">
         <f t="shared" si="15"/>
@@ -8567,7 +8605,7 @@
       </c>
       <c r="N32" s="10">
         <f t="shared" si="15"/>
-        <v>40604.5</v>
+        <v>46982.9</v>
       </c>
       <c r="O32" s="1" t="e">
         <f t="shared" si="15"/>
@@ -8587,7 +8625,7 @@
       </c>
       <c r="S32" s="10">
         <f t="shared" si="15"/>
-        <v>25325.285714285714</v>
+        <v>27013.135135135137</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8631,11 +8669,11 @@
       </c>
       <c r="K33" s="11">
         <f t="shared" si="16"/>
-        <v>5278.585</v>
-      </c>
-      <c r="L33" s="11" t="e">
+        <v>7502.3166666666666</v>
+      </c>
+      <c r="L33" s="11">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M33" s="11" t="e">
         <f t="shared" si="16"/>
@@ -8643,7 +8681,7 @@
       </c>
       <c r="N33" s="13">
         <f t="shared" si="16"/>
-        <v>5278.585</v>
+        <v>4501.3900000000003</v>
       </c>
       <c r="O33" s="11" t="e">
         <f t="shared" si="16"/>
@@ -8663,7 +8701,7 @@
       </c>
       <c r="S33" s="13">
         <f t="shared" si="16"/>
-        <v>3023.9511428571432</v>
+        <v>3040.7968918918918</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8709,9 +8747,9 @@
         <f t="shared" si="17"/>
         <v>2.0899238489042711</v>
       </c>
-      <c r="L34" s="23" t="e">
+      <c r="L34" s="23">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
+        <v>3.4826566923768216</v>
       </c>
       <c r="M34" s="23" t="e">
         <f t="shared" si="17"/>
@@ -8719,7 +8757,7 @@
       </c>
       <c r="N34" s="24">
         <f t="shared" si="17"/>
-        <v>2.0899238489042711</v>
+        <v>2.5882589760712653</v>
       </c>
       <c r="O34" s="23" t="e">
         <f t="shared" si="17"/>
@@ -8739,7 +8777,7 @@
       </c>
       <c r="S34" s="24">
         <f t="shared" si="17"/>
-        <v>1.0614177679910575</v>
+        <v>1.1520512150014086</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8783,11 +8821,11 @@
       </c>
       <c r="K35" s="18">
         <f t="shared" si="18"/>
-        <v>0.27169010035755525</v>
-      </c>
-      <c r="L35" s="18" t="e">
+        <v>0.38614612970726553</v>
+      </c>
+      <c r="L35" s="18">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M35" s="18" t="e">
         <f t="shared" si="18"/>
@@ -8795,7 +8833,7 @@
       </c>
       <c r="N35" s="19">
         <f t="shared" si="18"/>
-        <v>0.27169010035755525</v>
+        <v>0.24797879807967227</v>
       </c>
       <c r="O35" s="18" t="e">
         <f t="shared" si="18"/>
@@ -8815,7 +8853,7 @@
       </c>
       <c r="S35" s="19">
         <f t="shared" si="18"/>
-        <v>0.12673797677057969</v>
+        <v>0.12968334613334531</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8864,11 +8902,11 @@
       </c>
       <c r="K38" s="11">
         <f t="shared" si="19"/>
-        <v>9822.7166666666672</v>
-      </c>
-      <c r="L38" s="11" t="str">
+        <v>11487.008333333333</v>
+      </c>
+      <c r="L38" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M38" s="11" t="str">
         <f t="shared" si="19"/>
@@ -8876,7 +8914,7 @@
       </c>
       <c r="N38" s="13">
         <f t="shared" si="19"/>
-        <v>9822.7166666666672</v>
+        <v>6892.2049999999999</v>
       </c>
       <c r="O38" s="11" t="str">
         <f t="shared" si="19"/>
@@ -8896,7 +8934,7 @@
       </c>
       <c r="S38" s="13">
         <f t="shared" si="19"/>
-        <v>6358.0628908515773</v>
+        <v>6149.3263832379789</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8940,11 +8978,11 @@
       </c>
       <c r="K39" s="16">
         <f t="shared" si="20"/>
-        <v>0.50557770253780077</v>
-      </c>
-      <c r="L39" s="16" t="e">
+        <v>0.5912392140869962</v>
+      </c>
+      <c r="L39" s="16">
         <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M39" s="16" t="e">
         <f t="shared" si="20"/>
@@ -8952,7 +8990,7 @@
       </c>
       <c r="N39" s="17">
         <f t="shared" si="20"/>
-        <v>0.50557770253780077</v>
+        <v>0.37968732147596801</v>
       </c>
       <c r="O39" s="16" t="e">
         <f t="shared" si="20"/>
@@ -8972,7 +9010,7 @@
       </c>
       <c r="S39" s="17">
         <f t="shared" si="20"/>
-        <v>0.26647521368525623</v>
+        <v>0.26225533970083892</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9190,7 +9228,7 @@
       </c>
       <c r="K46" s="52">
         <f t="shared" si="22"/>
-        <v>0.27644971774317045</v>
+        <v>0.19450836297232632</v>
       </c>
       <c r="L46" s="52" t="e">
         <f t="shared" si="22"/>
@@ -9202,7 +9240,7 @@
       </c>
       <c r="N46" s="52">
         <f t="shared" si="22"/>
-        <v>0.27644971774317045</v>
+        <v>0.19450836297232632</v>
       </c>
       <c r="O46" s="52" t="e">
         <f t="shared" si="22"/>
@@ -9222,7 +9260,7 @@
       </c>
       <c r="S46" s="52">
         <f>+S44/S29</f>
-        <v>0.21406983238296842</v>
+        <v>0.20137666615396918</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -33905,7 +33943,9 @@
         <f t="shared" si="9"/>
         <v>384</v>
       </c>
-      <c r="F183" s="3"/>
+      <c r="F183" s="3">
+        <v>20531</v>
+      </c>
       <c r="G183" s="3"/>
       <c r="H183" s="3">
         <v>24572</v>
@@ -33942,7 +33982,9 @@
         <f t="shared" si="9"/>
         <v>240</v>
       </c>
-      <c r="F184" s="3"/>
+      <c r="F184" s="3">
+        <v>9694</v>
+      </c>
       <c r="G184" s="3"/>
       <c r="H184" s="3"/>
       <c r="I184" s="3">
@@ -33987,7 +34029,9 @@
         <f t="shared" si="9"/>
         <v>158</v>
       </c>
-      <c r="F185" s="3"/>
+      <c r="F185" s="3">
+        <v>4491</v>
+      </c>
       <c r="G185" s="3"/>
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
@@ -34022,7 +34066,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F186" s="3"/>
+      <c r="F186" s="3">
+        <v>727</v>
+      </c>
       <c r="G186" s="3"/>
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
@@ -34057,7 +34103,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F187" s="3"/>
+      <c r="F187" s="3">
+        <v>738</v>
+      </c>
       <c r="G187" s="3"/>
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
@@ -34092,7 +34140,9 @@
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
-      <c r="F188" s="3"/>
+      <c r="F188" s="3">
+        <v>9801</v>
+      </c>
       <c r="G188" s="3"/>
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
@@ -34127,7 +34177,9 @@
         <f t="shared" si="9"/>
         <v>169</v>
       </c>
-      <c r="F189" s="3"/>
+      <c r="F189" s="3">
+        <v>8751</v>
+      </c>
       <c r="G189" s="3"/>
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
@@ -34162,7 +34214,9 @@
         <f t="shared" si="9"/>
         <v>150</v>
       </c>
-      <c r="F190" s="3"/>
+      <c r="F190" s="3">
+        <v>9393</v>
+      </c>
       <c r="G190" s="3"/>
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
@@ -34197,7 +34251,9 @@
         <f t="shared" si="9"/>
         <v>379</v>
       </c>
-      <c r="F191" s="3"/>
+      <c r="F191" s="3">
+        <v>17847</v>
+      </c>
       <c r="G191" s="3"/>
       <c r="H191" s="3">
         <v>26506</v>
@@ -34234,7 +34290,9 @@
         <f t="shared" si="9"/>
         <v>172</v>
       </c>
-      <c r="F192" s="3"/>
+      <c r="F192" s="3">
+        <v>5278</v>
+      </c>
       <c r="G192" s="3"/>
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
@@ -34269,7 +34327,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F193" s="3"/>
+      <c r="F193" s="3">
+        <v>748</v>
+      </c>
       <c r="G193" s="3"/>
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
@@ -34304,7 +34364,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F194" s="3"/>
+      <c r="F194" s="3">
+        <v>712</v>
+      </c>
       <c r="G194" s="3"/>
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
@@ -34339,7 +34401,9 @@
         <f t="shared" ref="E195:E258" si="15">+D195-D194</f>
         <v>90</v>
       </c>
-      <c r="F195" s="3"/>
+      <c r="F195" s="3">
+        <v>12169</v>
+      </c>
       <c r="G195" s="3"/>
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
@@ -34374,7 +34438,9 @@
         <f t="shared" si="15"/>
         <v>121</v>
       </c>
-      <c r="F196" s="3"/>
+      <c r="F196" s="3">
+        <v>8049</v>
+      </c>
       <c r="G196" s="3"/>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
@@ -34402,12 +34468,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D197" s="3"/>
+      <c r="D197" s="3">
+        <v>975145</v>
+      </c>
       <c r="E197" s="3">
         <f t="shared" si="15"/>
-        <v>-974964</v>
-      </c>
-      <c r="F197" s="3"/>
+        <v>181</v>
+      </c>
+      <c r="F197" s="3">
+        <v>8007</v>
+      </c>
       <c r="G197" s="3"/>
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
@@ -34435,12 +34505,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D198" s="3"/>
+      <c r="D198" s="3">
+        <v>975504</v>
+      </c>
       <c r="E198" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F198" s="3"/>
+        <v>359</v>
+      </c>
+      <c r="F198" s="3">
+        <v>8024</v>
+      </c>
       <c r="G198" s="3"/>
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
@@ -34468,14 +34542,20 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D199" s="3"/>
+      <c r="D199" s="3">
+        <v>975672</v>
+      </c>
       <c r="E199" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F199" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="F199" s="3">
+        <v>6917</v>
+      </c>
       <c r="G199" s="3"/>
-      <c r="H199" s="3"/>
+      <c r="H199" s="3">
+        <v>15759.9</v>
+      </c>
       <c r="I199" s="3"/>
       <c r="J199" s="61"/>
       <c r="K199" s="61"/>
@@ -34501,12 +34581,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D200" s="3"/>
+      <c r="D200" s="3">
+        <v>975759</v>
+      </c>
       <c r="E200" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F200" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="F200" s="3">
+        <v>735</v>
+      </c>
       <c r="G200" s="3"/>
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
@@ -34534,12 +34618,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D201" s="3"/>
+      <c r="D201" s="3">
+        <v>975759</v>
+      </c>
       <c r="E201" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F201" s="3"/>
+      <c r="F201" s="3">
+        <v>717</v>
+      </c>
       <c r="G201" s="3"/>
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
@@ -34567,12 +34655,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D202" s="3"/>
+      <c r="D202" s="3">
+        <v>975759</v>
+      </c>
       <c r="E202" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F202" s="3"/>
+      <c r="F202" s="3">
+        <v>17429</v>
+      </c>
       <c r="G202" s="3"/>
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
@@ -34600,12 +34692,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D203" s="3"/>
+      <c r="D203" s="3">
+        <v>975880</v>
+      </c>
       <c r="E203" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F203" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="F203" s="3">
+        <v>9189</v>
+      </c>
       <c r="G203" s="3"/>
       <c r="H203" s="3"/>
       <c r="I203" s="3"/>
@@ -34633,12 +34729,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D204" s="3"/>
+      <c r="D204" s="3">
+        <v>976005</v>
+      </c>
       <c r="E204" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F204" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="F204" s="3">
+        <v>7993</v>
+      </c>
       <c r="G204" s="3"/>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
@@ -34666,14 +34766,20 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D205" s="3"/>
+      <c r="D205" s="3">
+        <v>976399</v>
+      </c>
       <c r="E205" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F205" s="3"/>
+        <v>394</v>
+      </c>
+      <c r="F205" s="3">
+        <v>12616</v>
+      </c>
       <c r="G205" s="3"/>
-      <c r="H205" s="3"/>
+      <c r="H205" s="3">
+        <v>20092.78</v>
+      </c>
       <c r="I205" s="3"/>
       <c r="J205" s="61"/>
       <c r="K205" s="61"/>
@@ -34699,12 +34805,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D206" s="3"/>
+      <c r="D206" s="3">
+        <v>976543</v>
+      </c>
       <c r="E206" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F206" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="F206" s="3">
+        <v>3393</v>
+      </c>
       <c r="G206" s="3"/>
       <c r="H206" s="3"/>
       <c r="I206" s="3"/>
@@ -34732,12 +34842,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D207" s="3"/>
+      <c r="D207" s="3">
+        <v>976597</v>
+      </c>
       <c r="E207" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F207" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="F207" s="3">
+        <v>0</v>
+      </c>
       <c r="G207" s="3"/>
       <c r="H207" s="3"/>
       <c r="I207" s="3"/>
@@ -34765,12 +34879,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D208" s="3"/>
+      <c r="D208" s="3">
+        <v>976597</v>
+      </c>
       <c r="E208" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F208" s="3"/>
+      <c r="F208" s="3">
+        <v>761</v>
+      </c>
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
@@ -34798,12 +34916,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D209" s="3"/>
+      <c r="D209" s="3">
+        <v>976700</v>
+      </c>
       <c r="E209" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F209" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="F209" s="3">
+        <v>10211</v>
+      </c>
       <c r="G209" s="3"/>
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
@@ -34831,14 +34953,20 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D210" s="3"/>
+      <c r="D210" s="3">
+        <v>977055</v>
+      </c>
       <c r="E210" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F210" s="3"/>
+        <v>355</v>
+      </c>
+      <c r="F210" s="3">
+        <v>10061</v>
+      </c>
       <c r="G210" s="3"/>
-      <c r="H210" s="3"/>
+      <c r="H210" s="3">
+        <v>16307.07</v>
+      </c>
       <c r="I210" s="3"/>
       <c r="J210" s="61"/>
       <c r="K210" s="61"/>
@@ -34864,12 +34992,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D211" s="3"/>
+      <c r="D211" s="3">
+        <v>977273</v>
+      </c>
       <c r="E211" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F211" s="3"/>
+        <v>218</v>
+      </c>
+      <c r="F211" s="3">
+        <v>4487</v>
+      </c>
       <c r="G211" s="3"/>
       <c r="H211" s="3"/>
       <c r="I211" s="3"/>
@@ -34897,14 +35029,20 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D212" s="3"/>
+      <c r="D212" s="3">
+        <v>977608</v>
+      </c>
       <c r="E212" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F212" s="3"/>
+        <v>335</v>
+      </c>
+      <c r="F212" s="3">
+        <v>10066</v>
+      </c>
       <c r="G212" s="3"/>
-      <c r="H212" s="3"/>
+      <c r="H212" s="3">
+        <v>13334.9</v>
+      </c>
       <c r="I212" s="3"/>
       <c r="J212" s="61"/>
       <c r="K212" s="61"/>
@@ -34930,12 +35068,16 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="D213" s="3"/>
+      <c r="D213" s="3">
+        <v>977730</v>
+      </c>
       <c r="E213" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F213" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="F213" s="3">
+        <v>0</v>
+      </c>
       <c r="G213" s="3"/>
       <c r="H213" s="3"/>
       <c r="I213" s="3"/>
@@ -34963,7 +35105,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D214" s="3"/>
+      <c r="D214" s="3">
+        <v>977730</v>
+      </c>
       <c r="E214" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -34995,7 +35139,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D215" s="3"/>
+      <c r="D215" s="3">
+        <v>977730</v>
+      </c>
       <c r="E215" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -35027,10 +35173,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D216" s="3"/>
+      <c r="D216" s="3">
+        <v>977800</v>
+      </c>
       <c r="E216" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
@@ -35059,10 +35207,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D217" s="3"/>
+      <c r="D217" s="3">
+        <v>977843</v>
+      </c>
       <c r="E217" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
@@ -35092,10 +35242,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D218" s="3"/>
+      <c r="D218" s="3">
+        <v>978003</v>
+      </c>
       <c r="E218" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -35125,14 +35277,18 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D219" s="3"/>
+      <c r="D219" s="3">
+        <v>978333</v>
+      </c>
       <c r="E219" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
-      <c r="H219" s="3"/>
+      <c r="H219" s="3">
+        <v>14860.96</v>
+      </c>
       <c r="I219" s="3"/>
       <c r="J219" s="61"/>
       <c r="K219" s="61"/>
@@ -35158,10 +35314,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D220" s="3"/>
+      <c r="D220" s="3">
+        <v>978403</v>
+      </c>
       <c r="E220" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -35191,10 +35349,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D221" s="3"/>
+      <c r="D221" s="3">
+        <v>978456</v>
+      </c>
       <c r="E221" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -35224,7 +35384,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D222" s="3"/>
+      <c r="D222" s="3">
+        <v>978456</v>
+      </c>
       <c r="E222" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -35257,10 +35419,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D223" s="3"/>
+      <c r="D223" s="3">
+        <v>978560</v>
+      </c>
       <c r="E223" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
@@ -35290,10 +35454,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D224" s="3"/>
+      <c r="D224" s="3">
+        <v>978631</v>
+      </c>
       <c r="E224" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
@@ -35323,10 +35489,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D225" s="3"/>
+      <c r="D225" s="3">
+        <v>978770</v>
+      </c>
       <c r="E225" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
@@ -35356,14 +35524,18 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D226" s="3"/>
+      <c r="D226" s="3">
+        <v>979180</v>
+      </c>
       <c r="E226" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
+      <c r="H226" s="3">
+        <v>18769.53</v>
+      </c>
       <c r="I226" s="3"/>
       <c r="J226" s="61"/>
       <c r="K226" s="61"/>
@@ -35389,10 +35561,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D227" s="3"/>
+      <c r="D227" s="3">
+        <v>979338</v>
+      </c>
       <c r="E227" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -35422,10 +35596,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D228" s="3"/>
+      <c r="D228" s="3">
+        <v>979420</v>
+      </c>
       <c r="E228" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -35455,10 +35631,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D229" s="3"/>
+      <c r="D229" s="3">
+        <v>0</v>
+      </c>
       <c r="E229" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-979420</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -35488,10 +35666,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D230" s="3"/>
+      <c r="D230" s="3">
+        <v>979420</v>
+      </c>
       <c r="E230" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>979420</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3"/>
@@ -35521,10 +35701,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D231" s="3"/>
+      <c r="D231" s="3">
+        <v>979526</v>
+      </c>
       <c r="E231" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
@@ -35554,10 +35736,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D232" s="3"/>
+      <c r="D232" s="3">
+        <v>979635</v>
+      </c>
       <c r="E232" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -35587,14 +35771,18 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D233" s="3"/>
+      <c r="D233" s="3">
+        <v>979987</v>
+      </c>
       <c r="E233" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
-      <c r="H233" s="3"/>
+      <c r="H233" s="3">
+        <v>13219.14</v>
+      </c>
       <c r="I233" s="3"/>
       <c r="J233" s="61"/>
       <c r="K233" s="61"/>
@@ -35620,10 +35808,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D234" s="3"/>
+      <c r="D234" s="3">
+        <v>980032</v>
+      </c>
       <c r="E234" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -35653,7 +35843,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D235" s="3"/>
+      <c r="D235" s="3">
+        <v>980032</v>
+      </c>
       <c r="E235" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -35686,10 +35878,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D236" s="3"/>
+      <c r="D236" s="3">
+        <v>980083</v>
+      </c>
       <c r="E236" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -35719,10 +35913,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D237" s="3"/>
+      <c r="D237" s="3">
+        <v>980157</v>
+      </c>
       <c r="E237" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3"/>
@@ -35752,10 +35948,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D238" s="3"/>
+      <c r="D238" s="3">
+        <v>980250</v>
+      </c>
       <c r="E238" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3"/>
@@ -35785,10 +35983,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D239" s="3"/>
+      <c r="D239" s="3">
+        <v>980329</v>
+      </c>
       <c r="E239" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
@@ -35818,14 +36018,18 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D240" s="3"/>
+      <c r="D240" s="3">
+        <v>980474</v>
+      </c>
       <c r="E240" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
-      <c r="H240" s="3"/>
+      <c r="H240" s="3">
+        <v>18101.36</v>
+      </c>
       <c r="I240" s="3"/>
       <c r="J240" s="61"/>
       <c r="K240" s="61"/>
@@ -35851,10 +36055,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D241" s="3"/>
+      <c r="D241" s="3">
+        <v>980529</v>
+      </c>
       <c r="E241" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -35884,7 +36090,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D242" s="3"/>
+      <c r="D242" s="3">
+        <v>980529</v>
+      </c>
       <c r="E242" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -35917,7 +36125,9 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D243" s="3"/>
+      <c r="D243" s="3">
+        <v>980529</v>
+      </c>
       <c r="E243" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -35950,10 +36160,12 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="D244" s="3"/>
+      <c r="D244" s="3">
+        <v>980552</v>
+      </c>
       <c r="E244" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
@@ -35982,10 +36194,12 @@
       <c r="C245">
         <v>9</v>
       </c>
-      <c r="D245" s="3"/>
+      <c r="D245" s="3">
+        <v>980641</v>
+      </c>
       <c r="E245" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
@@ -36014,10 +36228,12 @@
       <c r="C246">
         <v>9</v>
       </c>
-      <c r="D246" s="3"/>
+      <c r="D246" s="3">
+        <v>980779</v>
+      </c>
       <c r="E246" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
@@ -36046,7 +36262,9 @@
       <c r="C247">
         <v>9</v>
       </c>
-      <c r="D247" s="3"/>
+      <c r="D247" s="3">
+        <v>980779</v>
+      </c>
       <c r="E247" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -36078,10 +36296,12 @@
       <c r="C248">
         <v>9</v>
       </c>
-      <c r="D248" s="3"/>
+      <c r="D248" s="3">
+        <v>981194</v>
+      </c>
       <c r="E248" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
@@ -36110,7 +36330,9 @@
       <c r="C249">
         <v>9</v>
       </c>
-      <c r="D249" s="3"/>
+      <c r="D249" s="3">
+        <v>981194</v>
+      </c>
       <c r="E249" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -36142,7 +36364,9 @@
       <c r="C250">
         <v>9</v>
       </c>
-      <c r="D250" s="3"/>
+      <c r="D250" s="3">
+        <v>981194</v>
+      </c>
       <c r="E250" s="3">
         <f t="shared" si="15"/>
         <v>0</v>
@@ -36177,7 +36401,7 @@
       <c r="D251" s="3"/>
       <c r="E251" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-981194</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3"/>

--- a/consumo_628.xlsx
+++ b/consumo_628.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Departamentos\Contabilidad\03 Suministros_consumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0B47AF-D7B2-4B18-BDDE-84D7E59D2645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BBF815-DA98-4841-9653-C11464324102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frio cierre 25" sheetId="14" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="76">
   <si>
     <t>1T</t>
   </si>
@@ -255,6 +255,21 @@
   </si>
   <si>
     <t>Días Producción</t>
+  </si>
+  <si>
+    <t>Consumo T mWh elec</t>
+  </si>
+  <si>
+    <t>% Frio / Total consumo</t>
+  </si>
+  <si>
+    <t>Total gasto €</t>
+  </si>
+  <si>
+    <t>Ajuste 2025</t>
+  </si>
+  <si>
+    <t>% Variable / Total gasto '26</t>
   </si>
 </sst>
 </file>
@@ -499,7 +514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -620,6 +635,7 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2293,13 +2309,13 @@
         <v>78000</v>
       </c>
       <c r="P7" s="39"/>
-      <c r="R7" s="87" t="s">
+      <c r="R7" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="87"/>
-      <c r="T7" s="87"/>
-      <c r="U7" s="87"/>
-      <c r="V7" s="87"/>
+      <c r="S7" s="88"/>
+      <c r="T7" s="88"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="88"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -2589,11 +2605,11 @@
         <v>276673.54100185522</v>
       </c>
       <c r="P12" s="39"/>
-      <c r="R12" s="84" t="s">
+      <c r="R12" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="S12" s="85"/>
-      <c r="T12" s="86"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="87"/>
       <c r="U12" s="47">
         <f>+U10*S9</f>
         <v>-8283.0026496869687</v>
@@ -2615,11 +2631,11 @@
       <c r="N13" s="39"/>
       <c r="O13" s="20"/>
       <c r="P13" s="39"/>
-      <c r="R13" s="84" t="s">
+      <c r="R13" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="S13" s="85"/>
-      <c r="T13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="87"/>
       <c r="U13" s="47">
         <f>+U9*T10</f>
         <v>-5990.1364407635365</v>
@@ -2819,13 +2835,13 @@
         <v>2160.91</v>
       </c>
       <c r="P18" s="39"/>
-      <c r="R18" s="88" t="s">
+      <c r="R18" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="89"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -3133,11 +3149,11 @@
         <v>71999.000000000015</v>
       </c>
       <c r="P23" s="39"/>
-      <c r="R23" s="84" t="s">
+      <c r="R23" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="85"/>
-      <c r="T23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="87"/>
       <c r="U23" s="47">
         <f>+U21*S20</f>
         <v>-33537.857501708335</v>
@@ -3159,11 +3175,11 @@
       <c r="N24" s="39"/>
       <c r="O24" s="20"/>
       <c r="P24" s="39"/>
-      <c r="R24" s="84" t="s">
+      <c r="R24" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="S24" s="85"/>
-      <c r="T24" s="86"/>
+      <c r="S24" s="86"/>
+      <c r="T24" s="87"/>
       <c r="U24" s="47">
         <f>+U20*T21</f>
         <v>13037.816139863742</v>
@@ -3471,11 +3487,14 @@
   <dimension ref="A4:X36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="3.28515625" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.28515625" customWidth="1"/>
     <col min="24" max="24" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -3666,13 +3685,13 @@
         <v>52000</v>
       </c>
       <c r="P7" s="39"/>
-      <c r="R7" s="87" t="s">
+      <c r="R7" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="S7" s="87"/>
-      <c r="T7" s="87"/>
-      <c r="U7" s="87"/>
-      <c r="V7" s="87"/>
+      <c r="S7" s="88"/>
+      <c r="T7" s="88"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="88"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -3914,11 +3933,11 @@
         <v>182648.24959999998</v>
       </c>
       <c r="P12" s="39"/>
-      <c r="R12" s="84" t="s">
+      <c r="R12" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="S12" s="85"/>
-      <c r="T12" s="86"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="87"/>
       <c r="U12" s="47">
         <f>+U10*S9</f>
         <v>-14675.939970713576</v>
@@ -3940,11 +3959,11 @@
       <c r="N13" s="39"/>
       <c r="O13" s="20"/>
       <c r="P13" s="39"/>
-      <c r="R13" s="84" t="s">
+      <c r="R13" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="S13" s="85"/>
-      <c r="T13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="87"/>
       <c r="U13" s="47">
         <f>+U9*T10</f>
         <v>41823.480366730837</v>
@@ -4136,13 +4155,13 @@
         <v>1171.53</v>
       </c>
       <c r="P18" s="39"/>
-      <c r="R18" s="88" t="s">
+      <c r="R18" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="89"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -4398,11 +4417,11 @@
         <v>49796.71</v>
       </c>
       <c r="P23" s="39"/>
-      <c r="R23" s="84" t="s">
+      <c r="R23" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="S23" s="85"/>
-      <c r="T23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="87"/>
       <c r="U23" s="47">
         <f>+U21*S20</f>
         <v>-17684.019958395245</v>
@@ -4424,11 +4443,11 @@
       <c r="N24" s="39"/>
       <c r="O24" s="20"/>
       <c r="P24" s="39"/>
-      <c r="R24" s="84" t="s">
+      <c r="R24" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="S24" s="85"/>
-      <c r="T24" s="86"/>
+      <c r="S24" s="86"/>
+      <c r="T24" s="87"/>
       <c r="U24" s="47">
         <f>+U20*T21</f>
         <v>31669.036834748116</v>
@@ -4520,60 +4539,48 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="20">
-        <f t="shared" ref="B27:M27" si="12">+B20+B21</f>
-        <v>16102.560000000001</v>
-      </c>
-      <c r="C27" s="20">
-        <f t="shared" si="12"/>
-        <v>12979.78</v>
-      </c>
-      <c r="D27" s="20">
-        <f t="shared" si="12"/>
-        <v>13354.990000000002</v>
-      </c>
-      <c r="E27" s="20">
-        <f t="shared" si="12"/>
-        <v>16457.2</v>
-      </c>
-      <c r="F27" s="20">
-        <f t="shared" si="12"/>
-        <v>15057.740000000002</v>
-      </c>
-      <c r="G27" s="20">
-        <f t="shared" si="12"/>
-        <v>15657.420000000002</v>
-      </c>
-      <c r="H27" s="20">
-        <f t="shared" si="12"/>
-        <v>17597.53</v>
-      </c>
-      <c r="I27" s="20">
-        <f t="shared" si="12"/>
-        <v>18050.78</v>
-      </c>
-      <c r="J27" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B27" s="3">
+        <f>+'2026'!C29</f>
+        <v>41764.51</v>
+      </c>
+      <c r="C27" s="3">
+        <f>+'2026'!D29</f>
+        <v>18357.46</v>
+      </c>
+      <c r="D27" s="3">
+        <f>+'2026'!E29</f>
+        <v>28464.400000000001</v>
+      </c>
+      <c r="E27" s="3">
+        <f>+'2026'!G29</f>
+        <v>27974.48</v>
+      </c>
+      <c r="F27" s="3">
+        <f>+'2026'!H29</f>
+        <v>30886.49</v>
+      </c>
+      <c r="G27" s="3">
+        <f>+'2026'!I29</f>
+        <v>32557.73</v>
+      </c>
+      <c r="H27" s="3">
+        <f>+'2026'!K29</f>
+        <v>45013.9</v>
+      </c>
+      <c r="I27" s="3">
+        <f>+'2026'!L29</f>
+        <v>41074.1</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
       <c r="N27" s="39"/>
-      <c r="O27" s="20">
-        <f>+O20+O21</f>
-        <v>125258</v>
+      <c r="O27" s="3">
+        <f>SUM(B27:N27)</f>
+        <v>266093.07</v>
       </c>
       <c r="P27" s="39"/>
       <c r="U27">
@@ -4581,127 +4588,183 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="N28" s="39"/>
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <f>SUM(B28:N28)</f>
+        <v>-9000</v>
+      </c>
       <c r="P28" s="39"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B29" s="20">
-        <f>+B27-B14</f>
-        <v>1571.5288</v>
-      </c>
-      <c r="C29" s="20">
-        <f t="shared" ref="C29:M29" si="13">+C27-C14</f>
-        <v>-1551.2512000000006</v>
-      </c>
-      <c r="D29" s="20">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="3">
+        <f>+'2026'!C28/1000</f>
+        <v>267.45800000000003</v>
+      </c>
+      <c r="C29" s="3">
+        <f>+'2026'!D28/1000</f>
+        <v>176.55</v>
+      </c>
+      <c r="D29" s="3">
+        <f>+'2026'!E28/1000</f>
+        <v>248.86199999999999</v>
+      </c>
+      <c r="E29" s="3">
+        <f>+'2026'!G28/1000</f>
+        <v>295.35300000000001</v>
+      </c>
+      <c r="F29" s="3">
+        <f>+'2026'!H28/1000</f>
+        <v>287.488</v>
+      </c>
+      <c r="G29" s="3">
+        <f>+'2026'!I28/1000</f>
+        <v>253.43199999999999</v>
+      </c>
+      <c r="H29" s="3">
+        <f>+'2026'!K28/1000</f>
+        <v>243.62700000000001</v>
+      </c>
+      <c r="I29" s="3">
+        <f>+'2026'!L28/1000</f>
+        <v>226.202</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="3">
+        <f>SUM(B29:N29)</f>
+        <v>1998.972</v>
+      </c>
+      <c r="P29" s="39"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="51">
+        <f t="shared" ref="B30:I30" si="12">+B18/B29</f>
+        <v>0.46597970522474552</v>
+      </c>
+      <c r="C30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.39920702350608894</v>
+      </c>
+      <c r="D30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.51731481704719895</v>
+      </c>
+      <c r="E30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.63798234654802899</v>
+      </c>
+      <c r="F30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.62882624666073017</v>
+      </c>
+      <c r="G30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.65717825688942211</v>
+      </c>
+      <c r="H30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.65148772508794184</v>
+      </c>
+      <c r="I30" s="51">
+        <f t="shared" si="12"/>
+        <v>0.67727075799506631</v>
+      </c>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="51">
+        <f>+O18/O29</f>
+        <v>0.58606623804635583</v>
+      </c>
+      <c r="P30" s="39"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="51">
+        <f t="shared" ref="B31:I31" si="13">+B20/(B27+B28)</f>
+        <v>0.22159983469919126</v>
+      </c>
+      <c r="C31" s="51">
         <f t="shared" si="13"/>
-        <v>-1176.0411999999997</v>
-      </c>
-      <c r="E29" s="20">
+        <v>0.22540318758695377</v>
+      </c>
+      <c r="D31" s="51">
         <f t="shared" si="13"/>
-        <v>1926.1687999999995</v>
-      </c>
-      <c r="F29" s="20">
+        <v>0.15855032953443599</v>
+      </c>
+      <c r="E31" s="51">
         <f t="shared" si="13"/>
-        <v>526.70880000000034</v>
-      </c>
-      <c r="G29" s="20">
+        <v>0.27222132457868742</v>
+      </c>
+      <c r="F31" s="51">
         <f t="shared" si="13"/>
-        <v>1126.3888000000006</v>
-      </c>
-      <c r="H29" s="20">
+        <v>0.20124624067027364</v>
+      </c>
+      <c r="G31" s="51">
         <f t="shared" si="13"/>
-        <v>3066.4987999999976</v>
-      </c>
-      <c r="I29" s="20">
+        <v>0.20933492599146195</v>
+      </c>
+      <c r="H31" s="51">
         <f t="shared" si="13"/>
-        <v>3519.7487999999976</v>
-      </c>
-      <c r="J29" s="20">
+        <v>0.19450836297232632</v>
+      </c>
+      <c r="I31" s="51">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="20">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="20">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="20">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="39"/>
-      <c r="O29" s="20">
-        <f>+O14-O27</f>
-        <v>-9009.7504000000044</v>
-      </c>
-      <c r="P29" s="39"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B30" s="20">
-        <f>+B29</f>
-        <v>1571.5288</v>
-      </c>
-      <c r="C30" s="20">
-        <f>+B30+C29</f>
-        <v>20.277599999999438</v>
-      </c>
-      <c r="D30" s="20">
-        <f t="shared" ref="D30:M30" si="14">+C30+D29</f>
-        <v>-1155.7636000000002</v>
-      </c>
-      <c r="E30" s="20">
-        <f t="shared" si="14"/>
-        <v>770.40519999999924</v>
-      </c>
-      <c r="F30" s="20">
-        <f t="shared" si="14"/>
-        <v>1297.1139999999996</v>
-      </c>
-      <c r="G30" s="20">
-        <f t="shared" si="14"/>
-        <v>2423.5028000000002</v>
-      </c>
-      <c r="H30" s="20">
-        <f t="shared" si="14"/>
-        <v>5490.0015999999978</v>
-      </c>
-      <c r="I30" s="20">
-        <f t="shared" si="14"/>
-        <v>9009.7503999999954</v>
-      </c>
-      <c r="J30" s="20">
-        <f t="shared" si="14"/>
-        <v>9009.7503999999954</v>
-      </c>
-      <c r="K30" s="20">
-        <f t="shared" si="14"/>
-        <v>9009.7503999999954</v>
-      </c>
-      <c r="L30" s="20">
-        <f t="shared" si="14"/>
-        <v>9009.7503999999954</v>
-      </c>
-      <c r="M30" s="20">
-        <f t="shared" si="14"/>
-        <v>9009.7503999999954</v>
-      </c>
-      <c r="N30" s="39"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="39"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.22420040852994955</v>
+      </c>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
       <c r="N31" s="39"/>
+      <c r="O31" s="51">
+        <f>+O20/(O27+O28)</f>
+        <v>0.21207261634862426</v>
+      </c>
       <c r="P31" s="39"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="N32" s="39"/>
-      <c r="O32" s="20">
-        <v>-14400</v>
-      </c>
+      <c r="O32" s="20"/>
       <c r="P32" s="39"/>
     </row>
     <row r="33" spans="14:16" x14ac:dyDescent="0.25">
@@ -7226,9 +7289,9 @@
         <f>+K1/K29</f>
         <v>0</v>
       </c>
-      <c r="L3" s="51" t="e">
+      <c r="L3" s="51">
         <f>+L1/L29</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M3" s="51" t="e">
         <f>+M1/M29</f>
@@ -7420,11 +7483,13 @@
       <c r="K9" s="9">
         <v>219535</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1">
+        <v>124826</v>
+      </c>
       <c r="M9" s="8"/>
       <c r="N9" s="10">
         <f>SUM(K9:M9)</f>
-        <v>219535</v>
+        <v>344361</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="1"/>
@@ -7435,7 +7500,7 @@
       </c>
       <c r="S9" s="10">
         <f>F9+J9+N9+R9</f>
-        <v>2828634</v>
+        <v>2953460</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7471,11 +7536,13 @@
       <c r="K10" s="14">
         <v>11531.83</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="11">
+        <v>8152.62</v>
+      </c>
       <c r="M10" s="12"/>
       <c r="N10" s="13">
         <f>SUM(K10:M10)</f>
-        <v>11531.83</v>
+        <v>19684.45</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="11"/>
@@ -7486,7 +7553,7 @@
       </c>
       <c r="S10" s="13">
         <f>F10+J10+N10+R10</f>
-        <v>130243.03</v>
+        <v>138395.65</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7529,11 +7596,14 @@
         <f>+K10/K9</f>
         <v>5.252843510146446E-2</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="37">
+        <f>+L10/L9</f>
+        <v>6.5311874128787265E-2</v>
+      </c>
       <c r="M11" s="11"/>
       <c r="N11" s="13">
         <f t="shared" si="0"/>
-        <v>5.252843510146446E-2</v>
+        <v>5.7162251242155765E-2</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
@@ -7544,7 +7614,7 @@
       </c>
       <c r="S11" s="13">
         <f t="shared" si="0"/>
-        <v>4.6044497096478371E-2</v>
+        <v>4.6858819824883352E-2</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7601,7 +7671,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>31206.5</v>
       </c>
       <c r="M13" s="1" t="e">
         <f t="shared" si="1"/>
@@ -7609,7 +7679,7 @@
       </c>
       <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>21953.5</v>
+        <v>34436.1</v>
       </c>
       <c r="O13" s="1" t="e">
         <f t="shared" si="1"/>
@@ -7629,7 +7699,7 @@
       </c>
       <c r="S13" s="10">
         <f t="shared" si="1"/>
-        <v>38224.783783783787</v>
+        <v>39911.62162162162</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7677,7 +7747,7 @@
       </c>
       <c r="L14" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2038.155</v>
       </c>
       <c r="M14" s="11" t="e">
         <f t="shared" si="2"/>
@@ -7685,7 +7755,7 @@
       </c>
       <c r="N14" s="13">
         <f t="shared" si="2"/>
-        <v>1153.183</v>
+        <v>1968.4450000000002</v>
       </c>
       <c r="O14" s="11" t="e">
         <f t="shared" si="2"/>
@@ -7705,7 +7775,7 @@
       </c>
       <c r="S14" s="13">
         <f t="shared" si="2"/>
-        <v>1760.0409459459459</v>
+        <v>1870.2114864864864</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7753,7 +7823,7 @@
       </c>
       <c r="L15" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.9218490742019483</v>
       </c>
       <c r="M15" s="23" t="e">
         <f t="shared" si="3"/>
@@ -7761,7 +7831,7 @@
       </c>
       <c r="N15" s="24">
         <f t="shared" si="3"/>
-        <v>1.2094047713355396</v>
+        <v>1.8970635045066973</v>
       </c>
       <c r="O15" s="23" t="e">
         <f t="shared" si="3"/>
@@ -7781,7 +7851,7 @@
       </c>
       <c r="S15" s="24">
         <f>+S9/S5</f>
-        <v>1.6302035428681816</v>
+        <v>1.7021434924841672</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7829,7 +7899,7 @@
       </c>
       <c r="L16" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.125519564828804</v>
       </c>
       <c r="M16" s="18" t="e">
         <f t="shared" si="4"/>
@@ -7837,7 +7907,7 @@
       </c>
       <c r="N16" s="19">
         <f t="shared" si="4"/>
-        <v>6.3528140042500361E-2</v>
+        <v>0.10844042066693632</v>
       </c>
       <c r="O16" s="18" t="e">
         <f t="shared" si="4"/>
@@ -7857,7 +7927,7 @@
       </c>
       <c r="S16" s="19">
         <f t="shared" si="4"/>
-        <v>7.5061902296262736E-2</v>
+        <v>7.9760435230413276E-2</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
@@ -7902,11 +7972,13 @@
       <c r="K19" s="82">
         <v>4688</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="9">
+        <v>2822</v>
+      </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10">
         <f>SUM(K19:M19)</f>
-        <v>4688</v>
+        <v>7510</v>
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
@@ -7917,7 +7989,7 @@
       </c>
       <c r="S19" s="10">
         <f>F19+J19+N19+R19</f>
-        <v>40038</v>
+        <v>42860</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7956,11 +8028,13 @@
       <c r="K20" s="83">
         <v>12376.32</v>
       </c>
-      <c r="L20" s="14"/>
+      <c r="L20" s="14">
+        <v>7450.08</v>
+      </c>
       <c r="M20" s="14"/>
       <c r="N20" s="10">
         <f>SUM(K20:M20)</f>
-        <v>12376.32</v>
+        <v>19826.400000000001</v>
       </c>
       <c r="O20" s="14"/>
       <c r="P20" s="14"/>
@@ -7971,7 +8045,7 @@
       </c>
       <c r="S20" s="13">
         <f>F20+J20+N20+R20</f>
-        <v>99788.152359610453</v>
+        <v>107238.23235961047</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8011,9 +8085,9 @@
         <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
-      <c r="L21" s="20" t="e">
+      <c r="L21" s="20">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>2.64</v>
       </c>
       <c r="M21" s="20" t="e">
         <f t="shared" si="5"/>
@@ -8041,7 +8115,7 @@
       </c>
       <c r="S21" s="20">
         <f t="shared" si="5"/>
-        <v>2.4923360897050415</v>
+        <v>2.5020586178163899</v>
       </c>
       <c r="T21" s="20"/>
       <c r="U21" s="20"/>
@@ -8091,7 +8165,7 @@
       </c>
       <c r="L22" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>705.5</v>
       </c>
       <c r="M22" s="1" t="e">
         <f t="shared" si="6"/>
@@ -8099,7 +8173,7 @@
       </c>
       <c r="N22" s="13">
         <f>+N19/N4</f>
-        <v>468.8</v>
+        <v>751</v>
       </c>
       <c r="O22" s="1" t="e">
         <f t="shared" ref="O22:Q22" si="7">+O19/O4</f>
@@ -8119,7 +8193,7 @@
       </c>
       <c r="S22" s="13">
         <f>+S19/S4</f>
-        <v>541.05405405405406</v>
+        <v>579.18918918918916</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8167,7 +8241,7 @@
       </c>
       <c r="L23" s="11">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1862.52</v>
       </c>
       <c r="M23" s="11" t="e">
         <f t="shared" si="8"/>
@@ -8175,7 +8249,7 @@
       </c>
       <c r="N23" s="13">
         <f>+N20/N4</f>
-        <v>1237.6320000000001</v>
+        <v>1982.64</v>
       </c>
       <c r="O23" s="11" t="e">
         <f t="shared" ref="O23:Q23" si="9">+O20/O4</f>
@@ -8195,7 +8269,7 @@
       </c>
       <c r="S23" s="13">
         <f>+S20/S4</f>
-        <v>1348.4885454001412</v>
+        <v>1449.1653021568982</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8243,7 +8317,7 @@
       </c>
       <c r="L24" s="16">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>4.3448144516349943E-2</v>
       </c>
       <c r="M24" s="16" t="e">
         <f t="shared" si="10"/>
@@ -8251,7 +8325,7 @@
       </c>
       <c r="N24" s="24">
         <f>+N19/N5</f>
-        <v>2.582590278552855E-2</v>
+        <v>4.1372126689274619E-2</v>
       </c>
       <c r="O24" s="16" t="e">
         <f t="shared" ref="O24:Q24" si="11">+O19/O5</f>
@@ -8271,7 +8345,7 @@
       </c>
       <c r="S24" s="24">
         <f>+S19/S5</f>
-        <v>2.3074773706798495E-2</v>
+        <v>2.4701153930600517E-2</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8319,7 +8393,7 @@
       </c>
       <c r="L25" s="16">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.11470310152316385</v>
       </c>
       <c r="M25" s="16" t="e">
         <f t="shared" si="12"/>
@@ -8327,7 +8401,7 @@
       </c>
       <c r="N25" s="19">
         <f>+N20/N5</f>
-        <v>6.8180383353795365E-2</v>
+        <v>0.109222414459685</v>
       </c>
       <c r="O25" s="16" t="e">
         <f t="shared" ref="O25:Q25" si="13">+O20/O5</f>
@@ -8347,7 +8421,7 @@
       </c>
       <c r="S25" s="19">
         <f>+S20/S5</f>
-        <v>5.751009127123087E-2</v>
+        <v>6.1803735062068217E-2</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -8461,11 +8535,13 @@
       <c r="K29" s="12">
         <v>45013.9</v>
       </c>
-      <c r="L29" s="11"/>
+      <c r="L29" s="11">
+        <v>41074.1</v>
+      </c>
       <c r="M29" s="12"/>
       <c r="N29" s="13">
         <f>SUM(K29:M29)</f>
-        <v>45013.9</v>
+        <v>86088</v>
       </c>
       <c r="O29" s="14"/>
       <c r="P29" s="11"/>
@@ -8476,7 +8552,7 @@
       </c>
       <c r="S29" s="13">
         <f>F29+J29+N29+R29</f>
-        <v>225018.97</v>
+        <v>266093.07</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8519,11 +8595,14 @@
         <f>+K29/K28</f>
         <v>0.18476564584385147</v>
       </c>
-      <c r="L30" s="11"/>
+      <c r="L30" s="11">
+        <f>+L29/L28</f>
+        <v>0.18158150679481172</v>
+      </c>
       <c r="M30" s="11"/>
       <c r="N30" s="13">
         <f t="shared" si="14"/>
-        <v>9.5809113528539117E-2</v>
+        <v>0.18323262293302456</v>
       </c>
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
@@ -8534,7 +8613,7 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="14"/>
-        <v>0.11256734461513218</v>
+        <v>0.13311495608742893</v>
       </c>
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
@@ -8673,7 +8752,7 @@
       </c>
       <c r="L33" s="11">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>10268.525</v>
       </c>
       <c r="M33" s="11" t="e">
         <f t="shared" si="16"/>
@@ -8681,7 +8760,7 @@
       </c>
       <c r="N33" s="13">
         <f t="shared" si="16"/>
-        <v>4501.3900000000003</v>
+        <v>8608.7999999999993</v>
       </c>
       <c r="O33" s="11" t="e">
         <f t="shared" si="16"/>
@@ -8701,7 +8780,7 @@
       </c>
       <c r="S33" s="13">
         <f t="shared" si="16"/>
-        <v>3040.7968918918918</v>
+        <v>3595.8522972972974</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8825,7 +8904,7 @@
       </c>
       <c r="L35" s="18">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>0.63238604985081825</v>
       </c>
       <c r="M35" s="18" t="e">
         <f t="shared" si="18"/>
@@ -8833,7 +8912,7 @@
       </c>
       <c r="N35" s="19">
         <f t="shared" si="18"/>
-        <v>0.24797879807967227</v>
+        <v>0.47425348101548243</v>
       </c>
       <c r="O35" s="18" t="e">
         <f t="shared" si="18"/>
@@ -8853,7 +8932,7 @@
       </c>
       <c r="S35" s="19">
         <f t="shared" si="18"/>
-        <v>0.12968334613334531</v>
+        <v>0.15335524689538169</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8906,7 +8985,7 @@
       </c>
       <c r="L38" s="11">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>14169.2</v>
       </c>
       <c r="M38" s="11" t="str">
         <f t="shared" si="19"/>
@@ -8914,7 +8993,7 @@
       </c>
       <c r="N38" s="13">
         <f t="shared" si="19"/>
-        <v>6892.2049999999999</v>
+        <v>12559.884999999998</v>
       </c>
       <c r="O38" s="11" t="str">
         <f t="shared" si="19"/>
@@ -8934,7 +9013,7 @@
       </c>
       <c r="S38" s="13">
         <f t="shared" si="19"/>
-        <v>6149.3263832379789</v>
+        <v>6915.2290859406821</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8982,7 +9061,7 @@
       </c>
       <c r="L39" s="16">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.87260871620278613</v>
       </c>
       <c r="M39" s="16" t="e">
         <f t="shared" si="20"/>
@@ -8990,7 +9069,7 @@
       </c>
       <c r="N39" s="17">
         <f t="shared" si="20"/>
-        <v>0.37968732147596801</v>
+        <v>0.6919163161421038</v>
       </c>
       <c r="O39" s="16" t="e">
         <f t="shared" si="20"/>
@@ -9010,7 +9089,7 @@
       </c>
       <c r="S39" s="17">
         <f t="shared" si="20"/>
-        <v>0.26225533970083892</v>
+        <v>0.29491941718786319</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9059,11 +9138,13 @@
         <f>+'Frio cierre 26'!H18*1000</f>
         <v>158720</v>
       </c>
-      <c r="L43" s="1"/>
+      <c r="L43" s="1">
+        <v>153200</v>
+      </c>
       <c r="M43" s="1"/>
       <c r="N43" s="10">
         <f>SUM(K43:M43)</f>
-        <v>158720</v>
+        <v>311920</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="1"/>
@@ -9074,7 +9155,7 @@
       </c>
       <c r="S43" s="10">
         <f>F43+J43+N43+R43</f>
-        <v>1018330</v>
+        <v>1171530</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9117,11 +9198,13 @@
         <f>+'Frio cierre 26'!H20</f>
         <v>8755.58</v>
       </c>
-      <c r="L44" s="11"/>
+      <c r="L44" s="11">
+        <v>9208.83</v>
+      </c>
       <c r="M44" s="11"/>
       <c r="N44" s="13">
         <f>SUM(K44:M44)</f>
-        <v>8755.58</v>
+        <v>17964.41</v>
       </c>
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
@@ -9132,7 +9215,7 @@
       </c>
       <c r="S44" s="13">
         <f>F44+J44+N44+R44</f>
-        <v>45313.570000000007</v>
+        <v>54522.400000000009</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9175,11 +9258,14 @@
         <f>+K44/K43</f>
         <v>5.5163684475806454E-2</v>
       </c>
-      <c r="L45" s="11"/>
+      <c r="L45" s="11">
+        <f>+L44/L43</f>
+        <v>6.0109856396866841E-2</v>
+      </c>
       <c r="M45" s="11"/>
       <c r="N45" s="13">
         <f t="shared" si="21"/>
-        <v>5.5163684475806454E-2</v>
+        <v>5.7593004616568348E-2</v>
       </c>
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
@@ -9190,7 +9276,7 @@
       </c>
       <c r="S45" s="13">
         <f t="shared" si="21"/>
-        <v>4.4497923070124623E-2</v>
+        <v>4.6539482556998121E-2</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -9230,9 +9316,9 @@
         <f t="shared" si="22"/>
         <v>0.19450836297232632</v>
       </c>
-      <c r="L46" s="52" t="e">
+      <c r="L46" s="52">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>0.22420040852994955</v>
       </c>
       <c r="M46" s="52" t="e">
         <f t="shared" si="22"/>
@@ -9240,7 +9326,7 @@
       </c>
       <c r="N46" s="52">
         <f t="shared" si="22"/>
-        <v>0.19450836297232632</v>
+        <v>0.20867496050552922</v>
       </c>
       <c r="O46" s="52" t="e">
         <f t="shared" si="22"/>
@@ -9260,7 +9346,7 @@
       </c>
       <c r="S46" s="52">
         <f>+S44/S29</f>
-        <v>0.20137666615396918</v>
+        <v>0.20489973677255108</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -35112,6 +35198,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="F214" s="3">
+        <v>0</v>
+      </c>
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
@@ -35146,6 +35235,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="F215" s="3">
+        <v>0</v>
+      </c>
       <c r="G215" s="3"/>
       <c r="H215" s="3"/>
       <c r="I215" s="3"/>
@@ -35180,6 +35272,9 @@
         <f t="shared" si="15"/>
         <v>70</v>
       </c>
+      <c r="F216" s="3">
+        <v>9227</v>
+      </c>
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
@@ -35214,7 +35309,9 @@
         <f t="shared" si="15"/>
         <v>43</v>
       </c>
-      <c r="F217" s="3"/>
+      <c r="F217" s="3">
+        <v>6922</v>
+      </c>
       <c r="G217" s="3"/>
       <c r="H217" s="3"/>
       <c r="I217" s="3"/>
@@ -35249,7 +35346,9 @@
         <f t="shared" si="15"/>
         <v>160</v>
       </c>
-      <c r="F218" s="3"/>
+      <c r="F218" s="3">
+        <v>4613</v>
+      </c>
       <c r="G218" s="3"/>
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
@@ -35284,7 +35383,9 @@
         <f t="shared" si="15"/>
         <v>330</v>
       </c>
-      <c r="F219" s="3"/>
+      <c r="F219" s="3">
+        <v>6927</v>
+      </c>
       <c r="G219" s="3"/>
       <c r="H219" s="3">
         <v>14860.96</v>
@@ -35321,7 +35422,9 @@
         <f t="shared" si="15"/>
         <v>70</v>
       </c>
-      <c r="F220" s="3"/>
+      <c r="F220" s="3">
+        <v>1162</v>
+      </c>
       <c r="G220" s="3"/>
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
@@ -35356,7 +35459,9 @@
         <f t="shared" si="15"/>
         <v>53</v>
       </c>
-      <c r="F221" s="3"/>
+      <c r="F221" s="3">
+        <v>0</v>
+      </c>
       <c r="G221" s="3"/>
       <c r="H221" s="3"/>
       <c r="I221" s="3"/>
@@ -35391,7 +35496,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F222" s="3"/>
+      <c r="F222" s="3">
+        <v>761</v>
+      </c>
       <c r="G222" s="3"/>
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
@@ -35426,7 +35533,9 @@
         <f t="shared" si="15"/>
         <v>104</v>
       </c>
-      <c r="F223" s="3"/>
+      <c r="F223" s="3">
+        <v>5822</v>
+      </c>
       <c r="G223" s="3"/>
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
@@ -35461,7 +35570,9 @@
         <f t="shared" si="15"/>
         <v>71</v>
       </c>
-      <c r="F224" s="3"/>
+      <c r="F224" s="3">
+        <v>0</v>
+      </c>
       <c r="G224" s="3"/>
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
@@ -35496,7 +35607,9 @@
         <f t="shared" si="15"/>
         <v>139</v>
       </c>
-      <c r="F225" s="3"/>
+      <c r="F225" s="3">
+        <v>8146</v>
+      </c>
       <c r="G225" s="3"/>
       <c r="H225" s="3"/>
       <c r="I225" s="3"/>
@@ -35531,7 +35644,9 @@
         <f t="shared" si="15"/>
         <v>410</v>
       </c>
-      <c r="F226" s="3"/>
+      <c r="F226" s="3">
+        <v>10460</v>
+      </c>
       <c r="G226" s="3"/>
       <c r="H226" s="3">
         <v>18769.53</v>
@@ -35568,7 +35683,9 @@
         <f t="shared" si="15"/>
         <v>158</v>
       </c>
-      <c r="F227" s="3"/>
+      <c r="F227" s="3">
+        <v>0</v>
+      </c>
       <c r="G227" s="3"/>
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
@@ -35603,7 +35720,9 @@
         <f t="shared" si="15"/>
         <v>82</v>
       </c>
-      <c r="F228" s="3"/>
+      <c r="F228" s="3">
+        <v>0</v>
+      </c>
       <c r="G228" s="3"/>
       <c r="H228" s="3"/>
       <c r="I228" s="3"/>
@@ -35638,7 +35757,9 @@
         <f t="shared" si="15"/>
         <v>-979420</v>
       </c>
-      <c r="F229" s="3"/>
+      <c r="F229" s="3">
+        <v>0</v>
+      </c>
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
       <c r="I229" s="3"/>
@@ -35673,7 +35794,9 @@
         <f t="shared" si="15"/>
         <v>979420</v>
       </c>
-      <c r="F230" s="3"/>
+      <c r="F230" s="3">
+        <v>6991</v>
+      </c>
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
@@ -35708,7 +35831,9 @@
         <f t="shared" si="15"/>
         <v>106</v>
       </c>
-      <c r="F231" s="3"/>
+      <c r="F231" s="3">
+        <v>5825</v>
+      </c>
       <c r="G231" s="3"/>
       <c r="H231" s="3"/>
       <c r="I231" s="3"/>
@@ -35743,7 +35868,9 @@
         <f t="shared" si="15"/>
         <v>109</v>
       </c>
-      <c r="F232" s="3"/>
+      <c r="F232" s="3">
+        <v>2317</v>
+      </c>
       <c r="G232" s="3"/>
       <c r="H232" s="3"/>
       <c r="I232" s="3"/>
@@ -35778,7 +35905,9 @@
         <f t="shared" si="15"/>
         <v>352</v>
       </c>
-      <c r="F233" s="3"/>
+      <c r="F233" s="3">
+        <v>12558</v>
+      </c>
       <c r="G233" s="3"/>
       <c r="H233" s="3">
         <v>13219.14</v>
@@ -35815,7 +35944,9 @@
         <f t="shared" si="15"/>
         <v>45</v>
       </c>
-      <c r="F234" s="3"/>
+      <c r="F234" s="3">
+        <v>0</v>
+      </c>
       <c r="G234" s="3"/>
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
@@ -35850,7 +35981,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F235" s="3"/>
+      <c r="F235" s="3">
+        <v>745</v>
+      </c>
       <c r="G235" s="3"/>
       <c r="H235" s="3"/>
       <c r="I235" s="3"/>
@@ -35885,7 +36018,9 @@
         <f t="shared" si="15"/>
         <v>51</v>
       </c>
-      <c r="F236" s="3"/>
+      <c r="F236" s="3">
+        <v>751</v>
+      </c>
       <c r="G236" s="3"/>
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
@@ -35920,7 +36055,9 @@
         <f t="shared" si="15"/>
         <v>74</v>
       </c>
-      <c r="F237" s="3"/>
+      <c r="F237" s="3">
+        <v>4631</v>
+      </c>
       <c r="G237" s="3"/>
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
@@ -35955,7 +36092,9 @@
         <f t="shared" si="15"/>
         <v>93</v>
       </c>
-      <c r="F238" s="3"/>
+      <c r="F238" s="3">
+        <v>5757</v>
+      </c>
       <c r="G238" s="3"/>
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
@@ -35990,7 +36129,9 @@
         <f t="shared" si="15"/>
         <v>79</v>
       </c>
-      <c r="F239" s="3"/>
+      <c r="F239" s="3">
+        <v>5729</v>
+      </c>
       <c r="G239" s="3"/>
       <c r="H239" s="3"/>
       <c r="I239" s="3"/>
@@ -36025,7 +36166,9 @@
         <f t="shared" si="15"/>
         <v>145</v>
       </c>
-      <c r="F240" s="3"/>
+      <c r="F240" s="3">
+        <v>13611</v>
+      </c>
       <c r="G240" s="3"/>
       <c r="H240" s="3">
         <v>18101.36</v>
@@ -36062,7 +36205,9 @@
         <f t="shared" si="15"/>
         <v>55</v>
       </c>
-      <c r="F241" s="3"/>
+      <c r="F241" s="3">
+        <v>4533</v>
+      </c>
       <c r="G241" s="3"/>
       <c r="H241" s="3"/>
       <c r="I241" s="3"/>
@@ -36097,7 +36242,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F242" s="3"/>
+      <c r="F242" s="3">
+        <v>753</v>
+      </c>
       <c r="G242" s="3"/>
       <c r="H242" s="3"/>
       <c r="I242" s="3"/>
@@ -36132,7 +36279,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F243" s="3"/>
+      <c r="F243" s="3">
+        <v>752</v>
+      </c>
       <c r="G243" s="3"/>
       <c r="H243" s="3"/>
       <c r="I243" s="3"/>
@@ -36167,7 +36316,9 @@
         <f t="shared" si="15"/>
         <v>23</v>
       </c>
-      <c r="F244" s="3"/>
+      <c r="F244" s="3">
+        <v>5833</v>
+      </c>
       <c r="G244" s="3"/>
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
